--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E0BE7B-457A-4EF5-84CB-7681CB94F12F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3600D42-D9C4-46E9-BCDF-FD57CC0CE849}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="417">
   <si>
     <t>Lecke</t>
   </si>
@@ -881,6 +881,405 @@
   </si>
   <si>
     <t>Hogy néz ki</t>
+  </si>
+  <si>
+    <t>1a</t>
+  </si>
+  <si>
+    <t>boy</t>
+  </si>
+  <si>
+    <t>fiú</t>
+  </si>
+  <si>
+    <t>girl</t>
+  </si>
+  <si>
+    <t>lány</t>
+  </si>
+  <si>
+    <t>best friend</t>
+  </si>
+  <si>
+    <t>legjobb barát</t>
+  </si>
+  <si>
+    <t>friend</t>
+  </si>
+  <si>
+    <t>barát</t>
+  </si>
+  <si>
+    <t>classmate</t>
+  </si>
+  <si>
+    <t>osztálytárs</t>
+  </si>
+  <si>
+    <t>man</t>
+  </si>
+  <si>
+    <t>férfi</t>
+  </si>
+  <si>
+    <t>men</t>
+  </si>
+  <si>
+    <t>férfiak</t>
+  </si>
+  <si>
+    <t>child</t>
+  </si>
+  <si>
+    <t>gyerek</t>
+  </si>
+  <si>
+    <t>children</t>
+  </si>
+  <si>
+    <t>gyerekek</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>val, vel</t>
+  </si>
+  <si>
+    <t>also</t>
+  </si>
+  <si>
+    <t>szintén, is</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>új</t>
+  </si>
+  <si>
+    <t>meet</t>
+  </si>
+  <si>
+    <t>találkozni</t>
+  </si>
+  <si>
+    <t>cool</t>
+  </si>
+  <si>
+    <t>menő</t>
+  </si>
+  <si>
+    <t>video game</t>
+  </si>
+  <si>
+    <t>videójáték</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t>számítógép</t>
+  </si>
+  <si>
+    <t>love</t>
+  </si>
+  <si>
+    <t>szeret</t>
+  </si>
+  <si>
+    <t>gadget</t>
+  </si>
+  <si>
+    <t>kütyü</t>
+  </si>
+  <si>
+    <t>very</t>
+  </si>
+  <si>
+    <t>cute</t>
+  </si>
+  <si>
+    <t>aranyos</t>
+  </si>
+  <si>
+    <t>family tree</t>
+  </si>
+  <si>
+    <t>családfa</t>
+  </si>
+  <si>
+    <t>me</t>
+  </si>
+  <si>
+    <t>én, engem</t>
+  </si>
+  <si>
+    <t>baby</t>
+  </si>
+  <si>
+    <t>kisbaba</t>
+  </si>
+  <si>
+    <t>brother</t>
+  </si>
+  <si>
+    <t>fiútestvér</t>
+  </si>
+  <si>
+    <t>father</t>
+  </si>
+  <si>
+    <t>apa</t>
+  </si>
+  <si>
+    <t>dad</t>
+  </si>
+  <si>
+    <t>grandfather</t>
+  </si>
+  <si>
+    <t>grandmother</t>
+  </si>
+  <si>
+    <t>nagymama</t>
+  </si>
+  <si>
+    <t>mother</t>
+  </si>
+  <si>
+    <t>anya</t>
+  </si>
+  <si>
+    <t>mum</t>
+  </si>
+  <si>
+    <t>parents</t>
+  </si>
+  <si>
+    <t>szülők</t>
+  </si>
+  <si>
+    <t>sister</t>
+  </si>
+  <si>
+    <t>lánytestvér</t>
+  </si>
+  <si>
+    <t>uncle</t>
+  </si>
+  <si>
+    <t>nagybácsi</t>
+  </si>
+  <si>
+    <t>aunt</t>
+  </si>
+  <si>
+    <t>nagynéni</t>
+  </si>
+  <si>
+    <t>cousin</t>
+  </si>
+  <si>
+    <t>unokatestvér</t>
+  </si>
+  <si>
+    <t>grandparents</t>
+  </si>
+  <si>
+    <t>nagyszülők</t>
+  </si>
+  <si>
+    <t>This is</t>
+  </si>
+  <si>
+    <t>Ez</t>
+  </si>
+  <si>
+    <t>1b</t>
+  </si>
+  <si>
+    <t>favourite</t>
+  </si>
+  <si>
+    <t>kedvenc</t>
+  </si>
+  <si>
+    <t>be good</t>
+  </si>
+  <si>
+    <t>jó valamiben</t>
+  </si>
+  <si>
+    <t>bad at</t>
+  </si>
+  <si>
+    <t>rossz valamiben</t>
+  </si>
+  <si>
+    <t>great</t>
+  </si>
+  <si>
+    <t>nagyszerű</t>
+  </si>
+  <si>
+    <t>kids</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>nem</t>
+  </si>
+  <si>
+    <t>win</t>
+  </si>
+  <si>
+    <t>győzni</t>
+  </si>
+  <si>
+    <t>puzzle</t>
+  </si>
+  <si>
+    <t>kirakó</t>
+  </si>
+  <si>
+    <t>here is</t>
+  </si>
+  <si>
+    <t>itt van</t>
+  </si>
+  <si>
+    <t>basketball</t>
+  </si>
+  <si>
+    <t>kosárlabda</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>könnyű</t>
+  </si>
+  <si>
+    <t>difficult</t>
+  </si>
+  <si>
+    <t>nehéz</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>csapat, csoport</t>
+  </si>
+  <si>
+    <t>correct</t>
+  </si>
+  <si>
+    <t>helyes</t>
+  </si>
+  <si>
+    <t>be sure</t>
+  </si>
+  <si>
+    <t>biztos valamiben</t>
+  </si>
+  <si>
+    <t>prize</t>
+  </si>
+  <si>
+    <t>díj</t>
+  </si>
+  <si>
+    <t>competition</t>
+  </si>
+  <si>
+    <t>verseny</t>
+  </si>
+  <si>
+    <t>thanks</t>
+  </si>
+  <si>
+    <t>köszönöm</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>válasz</t>
+  </si>
+  <si>
+    <t>art</t>
+  </si>
+  <si>
+    <t>művészet, rajz</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>angol</t>
+  </si>
+  <si>
+    <t>geography</t>
+  </si>
+  <si>
+    <t>földrajz</t>
+  </si>
+  <si>
+    <t>history</t>
+  </si>
+  <si>
+    <t>történelem</t>
+  </si>
+  <si>
+    <t>maths</t>
+  </si>
+  <si>
+    <t>matematika</t>
+  </si>
+  <si>
+    <t>IT ( information technology)</t>
+  </si>
+  <si>
+    <t>informatika</t>
+  </si>
+  <si>
+    <t>music</t>
+  </si>
+  <si>
+    <t>zene</t>
+  </si>
+  <si>
+    <t>PE (physical education)</t>
+  </si>
+  <si>
+    <t>testnevelés</t>
+  </si>
+  <si>
+    <t>science</t>
+  </si>
+  <si>
+    <t>természettudományok</t>
+  </si>
+  <si>
+    <t>What's your favourite subject?</t>
+  </si>
+  <si>
+    <t>Mi a kedvenc tantárgyad?</t>
+  </si>
+  <si>
+    <t>What year are you in? I'M IN YEAR</t>
+  </si>
+  <si>
+    <t>Hanyadikos vagy? Én…</t>
+  </si>
+  <si>
+    <t>Come on</t>
+  </si>
+  <si>
+    <t>Gyerünk</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E74B09-1592-4B2F-8A8F-90DE63FDA08A}">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -1987,6 +2386,754 @@
       </c>
       <c r="C58" t="s">
         <v>282</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>284</v>
+      </c>
+      <c r="B59" t="s">
+        <v>285</v>
+      </c>
+      <c r="C59" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B60" t="s">
+        <v>287</v>
+      </c>
+      <c r="C60" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B61" t="s">
+        <v>289</v>
+      </c>
+      <c r="C61" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B62" t="s">
+        <v>291</v>
+      </c>
+      <c r="C62" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B63" t="s">
+        <v>293</v>
+      </c>
+      <c r="C63" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B64" t="s">
+        <v>295</v>
+      </c>
+      <c r="C64" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B65" t="s">
+        <v>297</v>
+      </c>
+      <c r="C65" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B66" t="s">
+        <v>299</v>
+      </c>
+      <c r="C66" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B67" t="s">
+        <v>301</v>
+      </c>
+      <c r="C67" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B68" t="s">
+        <v>303</v>
+      </c>
+      <c r="C68" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B69" t="s">
+        <v>305</v>
+      </c>
+      <c r="C69" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B70" t="s">
+        <v>307</v>
+      </c>
+      <c r="C70" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B71" t="s">
+        <v>309</v>
+      </c>
+      <c r="C71" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B72" t="s">
+        <v>311</v>
+      </c>
+      <c r="C72" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B73" t="s">
+        <v>313</v>
+      </c>
+      <c r="C73" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B74" t="s">
+        <v>315</v>
+      </c>
+      <c r="C74" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B75" t="s">
+        <v>317</v>
+      </c>
+      <c r="C75" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B76" t="s">
+        <v>319</v>
+      </c>
+      <c r="C76" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B77" t="s">
+        <v>321</v>
+      </c>
+      <c r="C77" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B78" t="s">
+        <v>322</v>
+      </c>
+      <c r="C78" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B79" t="s">
+        <v>324</v>
+      </c>
+      <c r="C79" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B80" t="s">
+        <v>326</v>
+      </c>
+      <c r="C80" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B81" t="s">
+        <v>328</v>
+      </c>
+      <c r="C81" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B82" t="s">
+        <v>330</v>
+      </c>
+      <c r="C82" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B83" t="s">
+        <v>332</v>
+      </c>
+      <c r="C83" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B84" t="s">
+        <v>334</v>
+      </c>
+      <c r="C84" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B85" t="s">
+        <v>335</v>
+      </c>
+      <c r="C85" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B86" t="s">
+        <v>336</v>
+      </c>
+      <c r="C86" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B87" t="s">
+        <v>338</v>
+      </c>
+      <c r="C87" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B88" t="s">
+        <v>340</v>
+      </c>
+      <c r="C88" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B89" t="s">
+        <v>341</v>
+      </c>
+      <c r="C89" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B90" t="s">
+        <v>343</v>
+      </c>
+      <c r="C90" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B91" t="s">
+        <v>345</v>
+      </c>
+      <c r="C91" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B92" t="s">
+        <v>347</v>
+      </c>
+      <c r="C92" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B93" t="s">
+        <v>349</v>
+      </c>
+      <c r="C93" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B94" t="s">
+        <v>351</v>
+      </c>
+      <c r="C94" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B95" t="s">
+        <v>353</v>
+      </c>
+      <c r="C95" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>355</v>
+      </c>
+      <c r="B96" t="s">
+        <v>356</v>
+      </c>
+      <c r="C96" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B97" t="s">
+        <v>358</v>
+      </c>
+      <c r="C97" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B98" t="s">
+        <v>360</v>
+      </c>
+      <c r="C98" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B99" t="s">
+        <v>362</v>
+      </c>
+      <c r="C99" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B100" t="s">
+        <v>364</v>
+      </c>
+      <c r="C100" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B101" t="s">
+        <v>365</v>
+      </c>
+      <c r="C101" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B102" t="s">
+        <v>367</v>
+      </c>
+      <c r="C102" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B103" t="s">
+        <v>369</v>
+      </c>
+      <c r="C103" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B104" t="s">
+        <v>371</v>
+      </c>
+      <c r="C104" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B105" t="s">
+        <v>373</v>
+      </c>
+      <c r="C105" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B106" t="s">
+        <v>375</v>
+      </c>
+      <c r="C106" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B107" t="s">
+        <v>377</v>
+      </c>
+      <c r="C107" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B108" t="s">
+        <v>379</v>
+      </c>
+      <c r="C108" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B109" t="s">
+        <v>381</v>
+      </c>
+      <c r="C109" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B110" t="s">
+        <v>383</v>
+      </c>
+      <c r="C110" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B111" t="s">
+        <v>385</v>
+      </c>
+      <c r="C111" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B112" t="s">
+        <v>387</v>
+      </c>
+      <c r="C112" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B113" t="s">
+        <v>389</v>
+      </c>
+      <c r="C113" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B114" t="s">
+        <v>391</v>
+      </c>
+      <c r="C114" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B115" t="s">
+        <v>393</v>
+      </c>
+      <c r="C115" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B116" t="s">
+        <v>395</v>
+      </c>
+      <c r="C116" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B117" t="s">
+        <v>397</v>
+      </c>
+      <c r="C117" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B118" t="s">
+        <v>399</v>
+      </c>
+      <c r="C118" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B119" t="s">
+        <v>401</v>
+      </c>
+      <c r="C119" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B120" t="s">
+        <v>403</v>
+      </c>
+      <c r="C120" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B121" t="s">
+        <v>405</v>
+      </c>
+      <c r="C121" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B122" t="s">
+        <v>407</v>
+      </c>
+      <c r="C122" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B123" t="s">
+        <v>409</v>
+      </c>
+      <c r="C123" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B124" t="s">
+        <v>411</v>
+      </c>
+      <c r="C124" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B125" t="s">
+        <v>413</v>
+      </c>
+      <c r="C125" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B126" t="s">
+        <v>415</v>
+      </c>
+      <c r="C126" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>

--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3600D42-D9C4-46E9-BCDF-FD57CC0CE849}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9336A8F3-C612-4ACA-AD68-021718CDDE3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
@@ -1747,1392 +1747,1504 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E74B09-1592-4B2F-8A8F-90DE63FDA08A}">
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>89</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>91</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>93</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>95</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>97</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>99</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>101</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>103</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>105</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>107</v>
       </c>
       <c r="C12" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>108</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>110</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>112</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>114</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>116</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>118</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>120</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>122</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>123</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>125</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>127</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>129</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>131</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>133</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>19</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>135</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>137</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>223</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>224</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>226</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>228</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>230</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>233</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>235</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>237</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>239</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>243</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>245</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>247</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>223</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>249</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>251</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>252</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>254</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>256</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>258</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>260</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>262</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>264</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>266</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>268</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>270</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>272</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>274</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>276</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>278</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>251</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>280</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>281</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>284</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
         <v>285</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
         <v>287</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
         <v>289</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1">
+        <v>3</v>
+      </c>
+      <c r="C62" t="s">
         <v>291</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
         <v>293</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1">
+        <v>5</v>
+      </c>
+      <c r="C64" t="s">
         <v>295</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1">
+        <v>5</v>
+      </c>
+      <c r="C65" t="s">
         <v>297</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1">
+        <v>6</v>
+      </c>
+      <c r="C66" t="s">
         <v>299</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
         <v>301</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
         <v>303</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
         <v>305</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
         <v>307</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
         <v>309</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
         <v>311</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
         <v>313</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
         <v>315</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
         <v>317</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
         <v>319</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1">
+        <v>16</v>
+      </c>
+      <c r="C77" t="s">
         <v>321</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1">
+        <v>17</v>
+      </c>
+      <c r="C78" t="s">
         <v>322</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1">
+        <v>18</v>
+      </c>
+      <c r="C79" t="s">
         <v>324</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1">
+        <v>19</v>
+      </c>
+      <c r="C80" t="s">
         <v>326</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1">
+        <v>20</v>
+      </c>
+      <c r="C81" t="s">
         <v>328</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1">
+        <v>21</v>
+      </c>
+      <c r="C82" t="s">
         <v>330</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1">
+        <v>22</v>
+      </c>
+      <c r="C83" t="s">
         <v>332</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1">
+        <v>22</v>
+      </c>
+      <c r="C84" t="s">
         <v>334</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1">
+        <v>23</v>
+      </c>
+      <c r="C85" t="s">
         <v>335</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1">
+        <v>24</v>
+      </c>
+      <c r="C86" t="s">
         <v>336</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1">
+        <v>25</v>
+      </c>
+      <c r="C87" t="s">
         <v>338</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1">
+        <v>25</v>
+      </c>
+      <c r="C88" t="s">
         <v>340</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
         <v>341</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1">
+        <v>27</v>
+      </c>
+      <c r="C90" t="s">
         <v>343</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1">
+        <v>28</v>
+      </c>
+      <c r="C91" t="s">
         <v>345</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1">
+        <v>29</v>
+      </c>
+      <c r="C92" t="s">
         <v>347</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1">
+        <v>30</v>
+      </c>
+      <c r="C93" t="s">
         <v>349</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1">
+        <v>31</v>
+      </c>
+      <c r="C94" t="s">
         <v>351</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1">
+        <v>32</v>
+      </c>
+      <c r="C95" t="s">
         <v>353</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>355</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>356</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>358</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>360</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>362</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>364</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>365</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>367</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>369</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>371</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>373</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>375</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>377</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>379</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>381</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>383</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>385</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>387</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>389</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>391</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>393</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>395</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>397</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
         <v>399</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>401</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>403</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>405</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>407</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>409</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>411</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>413</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>415</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
         <v>416</v>
       </c>
     </row>

--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9336A8F3-C612-4ACA-AD68-021718CDDE3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E3B8A0-E539-4F08-B1C2-217A1E3933CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="423">
   <si>
     <t>Lecke</t>
   </si>
@@ -1280,6 +1280,24 @@
   </si>
   <si>
     <t>Gyerünk</t>
+  </si>
+  <si>
+    <t>woman</t>
+  </si>
+  <si>
+    <t>nő</t>
+  </si>
+  <si>
+    <t>women</t>
+  </si>
+  <si>
+    <t>nők</t>
+  </si>
+  <si>
+    <t>family</t>
+  </si>
+  <si>
+    <t>család</t>
   </si>
 </sst>
 </file>
@@ -1747,7 +1765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E74B09-1592-4B2F-8A8F-90DE63FDA08A}">
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.88671875" style="1"/>
@@ -2487,32 +2505,32 @@
         <v>298</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>284</v>
       </c>
       <c r="B66" s="1">
         <v>6</v>
       </c>
-      <c r="C66" t="s">
-        <v>299</v>
-      </c>
-      <c r="D66" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C66" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>284</v>
       </c>
       <c r="B67" s="1">
         <v>6</v>
       </c>
-      <c r="C67" t="s">
-        <v>301</v>
-      </c>
-      <c r="D67" t="s">
-        <v>302</v>
+      <c r="C67" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -2523,10 +2541,10 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D68" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2534,13 +2552,13 @@
         <v>284</v>
       </c>
       <c r="B69" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D69" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2548,13 +2566,13 @@
         <v>284</v>
       </c>
       <c r="B70" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D70" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -2562,13 +2580,13 @@
         <v>284</v>
       </c>
       <c r="B71" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D71" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2576,13 +2594,13 @@
         <v>284</v>
       </c>
       <c r="B72" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D72" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -2590,13 +2608,13 @@
         <v>284</v>
       </c>
       <c r="B73" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D73" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -2604,13 +2622,13 @@
         <v>284</v>
       </c>
       <c r="B74" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D74" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -2618,13 +2636,13 @@
         <v>284</v>
       </c>
       <c r="B75" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D75" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -2632,13 +2650,13 @@
         <v>284</v>
       </c>
       <c r="B76" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C76" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D76" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -2646,13 +2664,13 @@
         <v>284</v>
       </c>
       <c r="B77" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D77" t="s">
-        <v>238</v>
+        <v>318</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -2660,13 +2678,13 @@
         <v>284</v>
       </c>
       <c r="B78" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C78" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D78" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -2674,13 +2692,13 @@
         <v>284</v>
       </c>
       <c r="B79" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D79" t="s">
-        <v>325</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -2688,13 +2706,13 @@
         <v>284</v>
       </c>
       <c r="B80" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D80" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -2702,27 +2720,27 @@
         <v>284</v>
       </c>
       <c r="B81" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C81" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D81" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>284</v>
       </c>
       <c r="B82" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D82" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -2730,13 +2748,13 @@
         <v>284</v>
       </c>
       <c r="B83" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>332</v>
+        <v>421</v>
       </c>
       <c r="D83" t="s">
-        <v>333</v>
+        <v>422</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -2744,13 +2762,13 @@
         <v>284</v>
       </c>
       <c r="B84" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C84" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="D84" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -2758,13 +2776,13 @@
         <v>284</v>
       </c>
       <c r="B85" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D85" t="s">
-        <v>59</v>
+        <v>331</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2772,13 +2790,13 @@
         <v>284</v>
       </c>
       <c r="B86" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C86" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D86" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -2786,13 +2804,13 @@
         <v>284</v>
       </c>
       <c r="B87" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D87" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -2800,13 +2818,13 @@
         <v>284</v>
       </c>
       <c r="B88" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C88" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D88" t="s">
-        <v>339</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2814,13 +2832,13 @@
         <v>284</v>
       </c>
       <c r="B89" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C89" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D89" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -2828,13 +2846,13 @@
         <v>284</v>
       </c>
       <c r="B90" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D90" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -2842,13 +2860,13 @@
         <v>284</v>
       </c>
       <c r="B91" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D91" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -2856,13 +2874,13 @@
         <v>284</v>
       </c>
       <c r="B92" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C92" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -2870,13 +2888,13 @@
         <v>284</v>
       </c>
       <c r="B93" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C93" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -2884,13 +2902,13 @@
         <v>284</v>
       </c>
       <c r="B94" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C94" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -2898,353 +2916,488 @@
         <v>284</v>
       </c>
       <c r="B95" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C95" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>355</v>
+      <c r="A96" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B96" s="1">
+        <v>31</v>
       </c>
       <c r="C96" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D96" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>355</v>
+        <v>284</v>
+      </c>
+      <c r="B97" s="1">
+        <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B98" s="1">
+        <v>33</v>
+      </c>
+      <c r="C98" t="s">
+        <v>353</v>
+      </c>
+      <c r="D98" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>355</v>
       </c>
-      <c r="C98" t="s">
-        <v>360</v>
-      </c>
-      <c r="D98" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="1" t="s">
-        <v>355</v>
+      <c r="B99" s="1">
+        <v>34</v>
       </c>
       <c r="C99" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B100" s="1">
+        <v>35</v>
+      </c>
       <c r="C100" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D100" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B101" s="1">
+        <v>35</v>
+      </c>
       <c r="C101" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D101" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B102" s="1">
+        <v>36</v>
+      </c>
       <c r="C102" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D102" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B103" s="1">
+        <v>37</v>
+      </c>
       <c r="C103" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>302</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B104" s="1">
+        <v>38</v>
+      </c>
       <c r="C104" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B105" s="1">
+        <v>39</v>
+      </c>
       <c r="C105" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D105" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B106" s="1">
+        <v>40</v>
+      </c>
       <c r="C106" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D106" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B107" s="1">
+        <v>41</v>
+      </c>
       <c r="C107" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D107" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B108" s="1">
+        <v>42</v>
+      </c>
       <c r="C108" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="D108" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B109" s="1">
+        <v>43</v>
+      </c>
       <c r="C109" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D109" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B110" s="1">
+        <v>44</v>
+      </c>
       <c r="C110" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="D110" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B111" s="1">
+        <v>45</v>
+      </c>
       <c r="C111" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D111" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B112" s="1">
+        <v>46</v>
+      </c>
       <c r="C112" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D112" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B113" s="1">
+        <v>47</v>
+      </c>
       <c r="C113" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D113" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B114" s="1">
+        <v>48</v>
+      </c>
       <c r="C114" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D114" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B115" s="1">
+        <v>49</v>
+      </c>
       <c r="C115" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D115" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B116" s="1">
+        <v>50</v>
+      </c>
       <c r="C116" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D116" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B117" s="1">
+        <v>51</v>
+      </c>
       <c r="C117" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D117" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B118" s="1">
+        <v>52</v>
+      </c>
       <c r="C118" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D118" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B119" s="1">
+        <v>53</v>
+      </c>
       <c r="C119" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D119" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B120" s="1">
+        <v>54</v>
+      </c>
       <c r="C120" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D120" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B121" s="1">
+        <v>55</v>
+      </c>
       <c r="C121" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D121" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B122" s="1">
+        <v>56</v>
+      </c>
       <c r="C122" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D122" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B123" s="1">
+        <v>57</v>
+      </c>
       <c r="C123" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D123" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B124" s="1">
+        <v>58</v>
+      </c>
       <c r="C124" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D124" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B125" s="1">
+        <v>59</v>
+      </c>
       <c r="C125" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D125" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>355</v>
       </c>
+      <c r="B126" s="1">
+        <v>60</v>
+      </c>
       <c r="C126" t="s">
+        <v>409</v>
+      </c>
+      <c r="D126" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B127" s="1">
+        <v>61</v>
+      </c>
+      <c r="C127" t="s">
+        <v>411</v>
+      </c>
+      <c r="D127" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B128" s="1">
+        <v>62</v>
+      </c>
+      <c r="C128" t="s">
+        <v>413</v>
+      </c>
+      <c r="D128" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B129" s="1">
+        <v>63</v>
+      </c>
+      <c r="C129" t="s">
         <v>415</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D129" t="s">
         <v>416</v>
       </c>
     </row>

--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E3B8A0-E539-4F08-B1C2-217A1E3933CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764AD62A-9817-47B0-964A-E33819D52920}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>

--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764AD62A-9817-47B0-964A-E33819D52920}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBE8B3F-AAAF-460E-BB32-FC2FCE539298}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="2" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
   <sheets>
     <sheet name="4. évf" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="600">
   <si>
     <t>Lecke</t>
   </si>
@@ -1298,6 +1298,537 @@
   </si>
   <si>
     <t>család</t>
+  </si>
+  <si>
+    <t>5a</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Hétfő</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Kedd</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Szerda</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Csütörtök</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Péntek</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Szombat</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Vasárnap</t>
+  </si>
+  <si>
+    <t>weekday</t>
+  </si>
+  <si>
+    <t>weekand</t>
+  </si>
+  <si>
+    <t>hétvége</t>
+  </si>
+  <si>
+    <t>hétköznap</t>
+  </si>
+  <si>
+    <t>What day is it?</t>
+  </si>
+  <si>
+    <t>Milyen nap van ma?</t>
+  </si>
+  <si>
+    <t>get up</t>
+  </si>
+  <si>
+    <t>felkel</t>
+  </si>
+  <si>
+    <t>zuhanyzik</t>
+  </si>
+  <si>
+    <t>have a shower</t>
+  </si>
+  <si>
+    <t>brush my teeth</t>
+  </si>
+  <si>
+    <t>megmosom a fogam</t>
+  </si>
+  <si>
+    <t>get dressed</t>
+  </si>
+  <si>
+    <t>felöltözik</t>
+  </si>
+  <si>
+    <t>go to school</t>
+  </si>
+  <si>
+    <t>iskolába megy</t>
+  </si>
+  <si>
+    <t>have breakfast</t>
+  </si>
+  <si>
+    <t>reggelizik</t>
+  </si>
+  <si>
+    <t>have lunch</t>
+  </si>
+  <si>
+    <t>ebédel</t>
+  </si>
+  <si>
+    <t>have dinner</t>
+  </si>
+  <si>
+    <t>vacsorázik</t>
+  </si>
+  <si>
+    <t>get home</t>
+  </si>
+  <si>
+    <t>hazamegy</t>
+  </si>
+  <si>
+    <t>do my homework</t>
+  </si>
+  <si>
+    <t>házi feladatomat csinálom</t>
+  </si>
+  <si>
+    <t>go to bed</t>
+  </si>
+  <si>
+    <t>lefekszik aludni</t>
+  </si>
+  <si>
+    <t>every</t>
+  </si>
+  <si>
+    <t>minden</t>
+  </si>
+  <si>
+    <t>make</t>
+  </si>
+  <si>
+    <t>készít, csinál</t>
+  </si>
+  <si>
+    <t>want to</t>
+  </si>
+  <si>
+    <t>akar</t>
+  </si>
+  <si>
+    <t>early</t>
+  </si>
+  <si>
+    <t>korán</t>
+  </si>
+  <si>
+    <t>későn</t>
+  </si>
+  <si>
+    <t>fun</t>
+  </si>
+  <si>
+    <t>vicces</t>
+  </si>
+  <si>
+    <t>boring</t>
+  </si>
+  <si>
+    <t>unalmas</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>dolgozat</t>
+  </si>
+  <si>
+    <t>get ready</t>
+  </si>
+  <si>
+    <t>felkészül</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>osztály</t>
+  </si>
+  <si>
+    <t>javít</t>
+  </si>
+  <si>
+    <t>housework</t>
+  </si>
+  <si>
+    <t>házimunka</t>
+  </si>
+  <si>
+    <t>play</t>
+  </si>
+  <si>
+    <t>játszik</t>
+  </si>
+  <si>
+    <t>again</t>
+  </si>
+  <si>
+    <t>újra</t>
+  </si>
+  <si>
+    <t>study</t>
+  </si>
+  <si>
+    <t>tanul</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>keményen</t>
+  </si>
+  <si>
+    <t>then</t>
+  </si>
+  <si>
+    <t>aztán</t>
+  </si>
+  <si>
+    <t>learn</t>
+  </si>
+  <si>
+    <t>after</t>
+  </si>
+  <si>
+    <t>után</t>
+  </si>
+  <si>
+    <t>work</t>
+  </si>
+  <si>
+    <t>munka</t>
+  </si>
+  <si>
+    <t>watch TV</t>
+  </si>
+  <si>
+    <t>tévét néz</t>
+  </si>
+  <si>
+    <t>probably</t>
+  </si>
+  <si>
+    <t>valószínűleg</t>
+  </si>
+  <si>
+    <t>What about you?</t>
+  </si>
+  <si>
+    <t>És te?</t>
+  </si>
+  <si>
+    <t>go on trip</t>
+  </si>
+  <si>
+    <t>kirándulni megy</t>
+  </si>
+  <si>
+    <t>go on holiday</t>
+  </si>
+  <si>
+    <t>nyaralni megy</t>
+  </si>
+  <si>
+    <t>adventure holiday</t>
+  </si>
+  <si>
+    <t>kalandos nyaralás</t>
+  </si>
+  <si>
+    <t>beach</t>
+  </si>
+  <si>
+    <t>tengerpart</t>
+  </si>
+  <si>
+    <t>camping</t>
+  </si>
+  <si>
+    <t>kempingezés</t>
+  </si>
+  <si>
+    <t>city tour</t>
+  </si>
+  <si>
+    <t>városnéző túra</t>
+  </si>
+  <si>
+    <t>cruise</t>
+  </si>
+  <si>
+    <t>hajókirándulás</t>
+  </si>
+  <si>
+    <t>theme park holiday</t>
+  </si>
+  <si>
+    <t>vidámparkos kirándulás</t>
+  </si>
+  <si>
+    <t>backpack</t>
+  </si>
+  <si>
+    <t>hátizsák</t>
+  </si>
+  <si>
+    <t>forest</t>
+  </si>
+  <si>
+    <t>erdő</t>
+  </si>
+  <si>
+    <t>last week</t>
+  </si>
+  <si>
+    <t>múlt héten</t>
+  </si>
+  <si>
+    <t>last night</t>
+  </si>
+  <si>
+    <t>múlt éjjel</t>
+  </si>
+  <si>
+    <t>sound</t>
+  </si>
+  <si>
+    <t>hang</t>
+  </si>
+  <si>
+    <t>still</t>
+  </si>
+  <si>
+    <t>még mindig</t>
+  </si>
+  <si>
+    <t>story</t>
+  </si>
+  <si>
+    <t>történet</t>
+  </si>
+  <si>
+    <t>suddenly</t>
+  </si>
+  <si>
+    <t>hirtelen</t>
+  </si>
+  <si>
+    <t>tent</t>
+  </si>
+  <si>
+    <t>sátor</t>
+  </si>
+  <si>
+    <t>yesterday</t>
+  </si>
+  <si>
+    <t>tegnap</t>
+  </si>
+  <si>
+    <t>angry</t>
+  </si>
+  <si>
+    <t>mérges</t>
+  </si>
+  <si>
+    <t>bored</t>
+  </si>
+  <si>
+    <t>unott</t>
+  </si>
+  <si>
+    <t>excited</t>
+  </si>
+  <si>
+    <t>izgatott</t>
+  </si>
+  <si>
+    <t>sad</t>
+  </si>
+  <si>
+    <t>szomorú</t>
+  </si>
+  <si>
+    <t>scared</t>
+  </si>
+  <si>
+    <t>ijedt</t>
+  </si>
+  <si>
+    <t>surprised</t>
+  </si>
+  <si>
+    <t>meglepődött</t>
+  </si>
+  <si>
+    <t>worried</t>
+  </si>
+  <si>
+    <t>aggódik</t>
+  </si>
+  <si>
+    <t>What a !</t>
+  </si>
+  <si>
+    <t>Micsoda!</t>
+  </si>
+  <si>
+    <t>a bit</t>
+  </si>
+  <si>
+    <t>egy kicsit</t>
+  </si>
+  <si>
+    <t>anymore</t>
+  </si>
+  <si>
+    <t>többé</t>
+  </si>
+  <si>
+    <t>bear cub</t>
+  </si>
+  <si>
+    <t>medvebocs</t>
+  </si>
+  <si>
+    <t>5b</t>
+  </si>
+  <si>
+    <t>ago</t>
+  </si>
+  <si>
+    <t>ezelőtt</t>
+  </si>
+  <si>
+    <t>around</t>
+  </si>
+  <si>
+    <t>körül, körbe</t>
+  </si>
+  <si>
+    <t>in the beginning</t>
+  </si>
+  <si>
+    <t>kezdetben</t>
+  </si>
+  <si>
+    <t>istructor</t>
+  </si>
+  <si>
+    <t>oktató</t>
+  </si>
+  <si>
+    <t>shout</t>
+  </si>
+  <si>
+    <t>kiabál</t>
+  </si>
+  <si>
+    <t>ski resort</t>
+  </si>
+  <si>
+    <t>síparadicsom, sípálya</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>megáll, megállít</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>idő</t>
+  </si>
+  <si>
+    <t>down</t>
+  </si>
+  <si>
+    <t>le</t>
+  </si>
+  <si>
+    <t>magazine</t>
+  </si>
+  <si>
+    <t>magazin</t>
+  </si>
+  <si>
+    <t>What an experience</t>
+  </si>
+  <si>
+    <t>Micsoda élmény!</t>
+  </si>
+  <si>
+    <t>Red Sea</t>
+  </si>
+  <si>
+    <t>Vörös-tenger</t>
+  </si>
+  <si>
+    <t>best part</t>
+  </si>
+  <si>
+    <t>legjobb part</t>
+  </si>
+  <si>
+    <t>swin away</t>
+  </si>
+  <si>
+    <t>elúszik</t>
+  </si>
+  <si>
+    <t>that was it</t>
+  </si>
+  <si>
+    <t>ennyi volt</t>
+  </si>
+  <si>
+    <t>the Alps</t>
+  </si>
+  <si>
+    <t>Alpok</t>
   </si>
 </sst>
 </file>
@@ -1765,7 +2296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E74B09-1592-4B2F-8A8F-90DE63FDA08A}">
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.88671875" style="1"/>
@@ -3401,6 +3932,622 @@
         <v>416</v>
       </c>
     </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>423</v>
+      </c>
+      <c r="B130" s="1">
+        <v>1</v>
+      </c>
+      <c r="C130" t="s">
+        <v>424</v>
+      </c>
+      <c r="D130" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B131" s="1">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>426</v>
+      </c>
+      <c r="D131" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B132" s="1">
+        <v>3</v>
+      </c>
+      <c r="C132" t="s">
+        <v>428</v>
+      </c>
+      <c r="D132" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B133" s="1">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>430</v>
+      </c>
+      <c r="D133" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B134" s="1">
+        <v>5</v>
+      </c>
+      <c r="C134" t="s">
+        <v>432</v>
+      </c>
+      <c r="D134" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B135" s="1">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>434</v>
+      </c>
+      <c r="D135" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B136" s="1">
+        <v>7</v>
+      </c>
+      <c r="C136" t="s">
+        <v>436</v>
+      </c>
+      <c r="D136" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B137" s="1">
+        <v>8</v>
+      </c>
+      <c r="C137" t="s">
+        <v>439</v>
+      </c>
+      <c r="D137" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B138" s="1">
+        <v>9</v>
+      </c>
+      <c r="C138" t="s">
+        <v>438</v>
+      </c>
+      <c r="D138" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B139" s="1">
+        <v>10</v>
+      </c>
+      <c r="C139" t="s">
+        <v>442</v>
+      </c>
+      <c r="D139" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B140" s="1">
+        <v>11</v>
+      </c>
+      <c r="C140" t="s">
+        <v>444</v>
+      </c>
+      <c r="D140" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B141" s="1">
+        <v>12</v>
+      </c>
+      <c r="C141" t="s">
+        <v>447</v>
+      </c>
+      <c r="D141" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B142" s="1">
+        <v>13</v>
+      </c>
+      <c r="C142" t="s">
+        <v>448</v>
+      </c>
+      <c r="D142" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B143" s="1">
+        <v>14</v>
+      </c>
+      <c r="C143" t="s">
+        <v>450</v>
+      </c>
+      <c r="D143" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B144" s="1">
+        <v>15</v>
+      </c>
+      <c r="C144" t="s">
+        <v>452</v>
+      </c>
+      <c r="D144" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B145" s="1">
+        <v>16</v>
+      </c>
+      <c r="C145" t="s">
+        <v>454</v>
+      </c>
+      <c r="D145" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B146" s="1">
+        <v>16</v>
+      </c>
+      <c r="C146" t="s">
+        <v>456</v>
+      </c>
+      <c r="D146" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B147" s="1">
+        <v>16</v>
+      </c>
+      <c r="C147" t="s">
+        <v>458</v>
+      </c>
+      <c r="D147" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B148" s="1">
+        <v>17</v>
+      </c>
+      <c r="C148" t="s">
+        <v>460</v>
+      </c>
+      <c r="D148" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B149" s="1">
+        <v>18</v>
+      </c>
+      <c r="C149" t="s">
+        <v>462</v>
+      </c>
+      <c r="D149" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B150" s="1">
+        <v>19</v>
+      </c>
+      <c r="C150" t="s">
+        <v>464</v>
+      </c>
+      <c r="D150" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B151" s="1">
+        <v>20</v>
+      </c>
+      <c r="C151" t="s">
+        <v>466</v>
+      </c>
+      <c r="D151" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B152" s="1">
+        <v>21</v>
+      </c>
+      <c r="C152" t="s">
+        <v>468</v>
+      </c>
+      <c r="D152" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B153" s="1">
+        <v>22</v>
+      </c>
+      <c r="C153" t="s">
+        <v>470</v>
+      </c>
+      <c r="D153" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B154" s="1">
+        <v>23</v>
+      </c>
+      <c r="C154" t="s">
+        <v>472</v>
+      </c>
+      <c r="D154" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B155" s="1">
+        <v>24</v>
+      </c>
+      <c r="C155" t="s">
+        <v>123</v>
+      </c>
+      <c r="D155" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B156" s="1">
+        <v>25</v>
+      </c>
+      <c r="C156" t="s">
+        <v>475</v>
+      </c>
+      <c r="D156" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B157" s="1">
+        <v>26</v>
+      </c>
+      <c r="C157" t="s">
+        <v>477</v>
+      </c>
+      <c r="D157" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B158" s="1">
+        <v>27</v>
+      </c>
+      <c r="C158" t="s">
+        <v>479</v>
+      </c>
+      <c r="D158" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B159" s="1">
+        <v>28</v>
+      </c>
+      <c r="C159" t="s">
+        <v>481</v>
+      </c>
+      <c r="D159" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B160" s="1">
+        <v>29</v>
+      </c>
+      <c r="C160" t="s">
+        <v>483</v>
+      </c>
+      <c r="D160" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B161" s="1">
+        <v>30</v>
+      </c>
+      <c r="C161" t="s">
+        <v>381</v>
+      </c>
+      <c r="D161" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B162" s="1">
+        <v>31</v>
+      </c>
+      <c r="C162" t="s">
+        <v>486</v>
+      </c>
+      <c r="D162" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B163" s="1">
+        <v>32</v>
+      </c>
+      <c r="C163" t="s">
+        <v>488</v>
+      </c>
+      <c r="D163" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B164" s="1">
+        <v>33</v>
+      </c>
+      <c r="C164" t="s">
+        <v>490</v>
+      </c>
+      <c r="D164" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B165" s="1">
+        <v>34</v>
+      </c>
+      <c r="C165" t="s">
+        <v>492</v>
+      </c>
+      <c r="D165" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B166" s="1">
+        <v>35</v>
+      </c>
+      <c r="C166" t="s">
+        <v>494</v>
+      </c>
+      <c r="D166" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B167" s="1">
+        <v>36</v>
+      </c>
+      <c r="C167" t="s">
+        <v>496</v>
+      </c>
+      <c r="D167" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B168" s="1">
+        <v>37</v>
+      </c>
+      <c r="C168" t="s">
+        <v>498</v>
+      </c>
+      <c r="D168" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B169" s="1">
+        <v>38</v>
+      </c>
+      <c r="C169" t="s">
+        <v>499</v>
+      </c>
+      <c r="D169" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B170" s="1">
+        <v>39</v>
+      </c>
+      <c r="C170" t="s">
+        <v>501</v>
+      </c>
+      <c r="D170" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B171" s="1">
+        <v>40</v>
+      </c>
+      <c r="C171" t="s">
+        <v>503</v>
+      </c>
+      <c r="D171" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B172" s="1">
+        <v>41</v>
+      </c>
+      <c r="C172" t="s">
+        <v>505</v>
+      </c>
+      <c r="D172" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B173" s="1">
+        <v>42</v>
+      </c>
+      <c r="C173" t="s">
+        <v>507</v>
+      </c>
+      <c r="D173" t="s">
+        <v>508</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3408,849 +4555,1556 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15400D6-8F26-4BDF-8F2A-A84DB8BE5864}">
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="39.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="39.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>39</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>43</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>48</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>50</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>52</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>54</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>56</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>58</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>19</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>60</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>62</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>64</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>66</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>19</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>68</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>86</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>19</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>72</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>19</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>74</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>19</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>76</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>19</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>78</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>19</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>80</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>19</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>82</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>19</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>84</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="C52" s="1" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>222</v>
       </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>423</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>509</v>
+      </c>
+      <c r="D77" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>511</v>
+      </c>
+      <c r="D78" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B79" s="1">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>513</v>
+      </c>
+      <c r="D79" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B80" s="1">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>515</v>
+      </c>
+      <c r="D80" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B81" s="1">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>517</v>
+      </c>
+      <c r="D81" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B82" s="1">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>519</v>
+      </c>
+      <c r="D82" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B83" s="1">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>521</v>
+      </c>
+      <c r="D83" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B84" s="1">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>523</v>
+      </c>
+      <c r="D84" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B85" s="1">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>525</v>
+      </c>
+      <c r="D85" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B86" s="1">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>527</v>
+      </c>
+      <c r="D86" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B87" s="1">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>529</v>
+      </c>
+      <c r="D87" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B88" s="1">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>531</v>
+      </c>
+      <c r="D88" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B89" s="1">
+        <v>12</v>
+      </c>
+      <c r="C89" t="s">
+        <v>241</v>
+      </c>
+      <c r="D89" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B90" s="1">
+        <v>13</v>
+      </c>
+      <c r="C90" t="s">
+        <v>505</v>
+      </c>
+      <c r="D90" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B91" s="1">
+        <v>14</v>
+      </c>
+      <c r="C91" t="s">
+        <v>533</v>
+      </c>
+      <c r="D91" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B92" s="1">
+        <v>15</v>
+      </c>
+      <c r="C92" t="s">
+        <v>535</v>
+      </c>
+      <c r="D92" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B93" s="1">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
+        <v>537</v>
+      </c>
+      <c r="D93" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B94" s="1">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>539</v>
+      </c>
+      <c r="D94" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B95" s="1">
+        <v>18</v>
+      </c>
+      <c r="C95" t="s">
+        <v>541</v>
+      </c>
+      <c r="D95" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B96" s="1">
+        <v>19</v>
+      </c>
+      <c r="C96" t="s">
+        <v>543</v>
+      </c>
+      <c r="D96" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B97" s="1">
+        <v>20</v>
+      </c>
+      <c r="C97" t="s">
+        <v>545</v>
+      </c>
+      <c r="D97" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B98" s="1">
+        <v>21</v>
+      </c>
+      <c r="C98" t="s">
+        <v>547</v>
+      </c>
+      <c r="D98" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B99" s="1">
+        <v>22</v>
+      </c>
+      <c r="C99" t="s">
+        <v>549</v>
+      </c>
+      <c r="D99" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B100" s="1">
+        <v>23</v>
+      </c>
+      <c r="C100" t="s">
+        <v>551</v>
+      </c>
+      <c r="D100" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B101" s="1">
+        <v>24</v>
+      </c>
+      <c r="C101" t="s">
+        <v>553</v>
+      </c>
+      <c r="D101" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B102" s="1">
+        <v>25</v>
+      </c>
+      <c r="C102" t="s">
+        <v>555</v>
+      </c>
+      <c r="D102" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B103" s="1">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>557</v>
+      </c>
+      <c r="D103" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B104" s="1">
+        <v>27</v>
+      </c>
+      <c r="C104" t="s">
+        <v>559</v>
+      </c>
+      <c r="D104" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B105" s="1">
+        <v>28</v>
+      </c>
+      <c r="C105" t="s">
+        <v>561</v>
+      </c>
+      <c r="D105" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B106" s="1">
+        <v>29</v>
+      </c>
+      <c r="C106" t="s">
+        <v>563</v>
+      </c>
+      <c r="D106" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B107" s="1">
+        <v>30</v>
+      </c>
+      <c r="C107" t="s">
+        <v>565</v>
+      </c>
+      <c r="D107" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B108" s="1">
+        <v>31</v>
+      </c>
+      <c r="C108" t="s">
+        <v>568</v>
+      </c>
+      <c r="D108" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B109" s="1">
+        <v>32</v>
+      </c>
+      <c r="C109" t="s">
+        <v>570</v>
+      </c>
+      <c r="D109" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B110" s="1">
+        <v>33</v>
+      </c>
+      <c r="C110" t="s">
+        <v>572</v>
+      </c>
+      <c r="D110" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B111" s="1">
+        <v>34</v>
+      </c>
+      <c r="C111" t="s">
+        <v>574</v>
+      </c>
+      <c r="D111" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B112" s="1">
+        <v>35</v>
+      </c>
+      <c r="C112" t="s">
+        <v>576</v>
+      </c>
+      <c r="D112" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B113" s="1">
+        <v>36</v>
+      </c>
+      <c r="C113" t="s">
+        <v>578</v>
+      </c>
+      <c r="D113" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B114" s="1">
+        <v>37</v>
+      </c>
+      <c r="C114" t="s">
+        <v>580</v>
+      </c>
+      <c r="D114" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B115" s="1">
+        <v>38</v>
+      </c>
+      <c r="C115" t="s">
+        <v>582</v>
+      </c>
+      <c r="D115" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B116" s="1">
+        <v>39</v>
+      </c>
+      <c r="C116" t="s">
+        <v>584</v>
+      </c>
+      <c r="D116" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B117" s="1">
+        <v>40</v>
+      </c>
+      <c r="C117" t="s">
+        <v>586</v>
+      </c>
+      <c r="D117" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B118" s="1">
+        <v>41</v>
+      </c>
+      <c r="C118" t="s">
+        <v>588</v>
+      </c>
+      <c r="D118" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B119" s="1">
+        <v>42</v>
+      </c>
+      <c r="C119" t="s">
+        <v>590</v>
+      </c>
+      <c r="D119" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B120" s="1">
+        <v>43</v>
+      </c>
+      <c r="C120" t="s">
+        <v>592</v>
+      </c>
+      <c r="D120" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B121" s="1">
+        <v>44</v>
+      </c>
+      <c r="C121" t="s">
+        <v>594</v>
+      </c>
+      <c r="D121" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B122" s="1">
+        <v>45</v>
+      </c>
+      <c r="C122" t="s">
+        <v>596</v>
+      </c>
+      <c r="D122" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B123" s="1">
+        <v>46</v>
+      </c>
+      <c r="C123" t="s">
+        <v>598</v>
+      </c>
+      <c r="D123" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="1"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="1"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="1"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="1"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="1"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="1"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="1"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="1"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="1"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="1"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="1"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="1"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="1"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="1"/>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="1"/>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBE8B3F-AAAF-460E-BB32-FC2FCE539298}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03B1E8B-0EF2-49E1-8F03-3CE8852F8571}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="2" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
   <sheets>
     <sheet name="4. évf" sheetId="1" r:id="rId1"/>
@@ -1348,9 +1348,6 @@
     <t>weekday</t>
   </si>
   <si>
-    <t>weekand</t>
-  </si>
-  <si>
     <t>hétvége</t>
   </si>
   <si>
@@ -1829,6 +1826,9 @@
   </si>
   <si>
     <t>Alpok</t>
+  </si>
+  <si>
+    <t>weekend</t>
   </si>
 </sst>
 </file>
@@ -4038,10 +4038,10 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
+        <v>599</v>
+      </c>
+      <c r="D137" t="s">
         <v>439</v>
-      </c>
-      <c r="D137" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -4055,7 +4055,7 @@
         <v>438</v>
       </c>
       <c r="D138" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -4066,10 +4066,10 @@
         <v>10</v>
       </c>
       <c r="C139" t="s">
+        <v>441</v>
+      </c>
+      <c r="D139" t="s">
         <v>442</v>
-      </c>
-      <c r="D139" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -4080,10 +4080,10 @@
         <v>11</v>
       </c>
       <c r="C140" t="s">
+        <v>443</v>
+      </c>
+      <c r="D140" t="s">
         <v>444</v>
-      </c>
-      <c r="D140" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -4094,10 +4094,10 @@
         <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D141" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -4108,10 +4108,10 @@
         <v>13</v>
       </c>
       <c r="C142" t="s">
+        <v>447</v>
+      </c>
+      <c r="D142" t="s">
         <v>448</v>
-      </c>
-      <c r="D142" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -4122,10 +4122,10 @@
         <v>14</v>
       </c>
       <c r="C143" t="s">
+        <v>449</v>
+      </c>
+      <c r="D143" t="s">
         <v>450</v>
-      </c>
-      <c r="D143" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -4136,10 +4136,10 @@
         <v>15</v>
       </c>
       <c r="C144" t="s">
+        <v>451</v>
+      </c>
+      <c r="D144" t="s">
         <v>452</v>
-      </c>
-      <c r="D144" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
@@ -4150,10 +4150,10 @@
         <v>16</v>
       </c>
       <c r="C145" t="s">
+        <v>453</v>
+      </c>
+      <c r="D145" t="s">
         <v>454</v>
-      </c>
-      <c r="D145" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -4164,10 +4164,10 @@
         <v>16</v>
       </c>
       <c r="C146" t="s">
+        <v>455</v>
+      </c>
+      <c r="D146" t="s">
         <v>456</v>
-      </c>
-      <c r="D146" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -4178,10 +4178,10 @@
         <v>16</v>
       </c>
       <c r="C147" t="s">
+        <v>457</v>
+      </c>
+      <c r="D147" t="s">
         <v>458</v>
-      </c>
-      <c r="D147" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -4192,10 +4192,10 @@
         <v>17</v>
       </c>
       <c r="C148" t="s">
+        <v>459</v>
+      </c>
+      <c r="D148" t="s">
         <v>460</v>
-      </c>
-      <c r="D148" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
@@ -4206,10 +4206,10 @@
         <v>18</v>
       </c>
       <c r="C149" t="s">
+        <v>461</v>
+      </c>
+      <c r="D149" t="s">
         <v>462</v>
-      </c>
-      <c r="D149" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -4220,10 +4220,10 @@
         <v>19</v>
       </c>
       <c r="C150" t="s">
+        <v>463</v>
+      </c>
+      <c r="D150" t="s">
         <v>464</v>
-      </c>
-      <c r="D150" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -4234,10 +4234,10 @@
         <v>20</v>
       </c>
       <c r="C151" t="s">
+        <v>465</v>
+      </c>
+      <c r="D151" t="s">
         <v>466</v>
-      </c>
-      <c r="D151" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
@@ -4248,10 +4248,10 @@
         <v>21</v>
       </c>
       <c r="C152" t="s">
+        <v>467</v>
+      </c>
+      <c r="D152" t="s">
         <v>468</v>
-      </c>
-      <c r="D152" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -4262,10 +4262,10 @@
         <v>22</v>
       </c>
       <c r="C153" t="s">
+        <v>469</v>
+      </c>
+      <c r="D153" t="s">
         <v>470</v>
-      </c>
-      <c r="D153" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -4276,10 +4276,10 @@
         <v>23</v>
       </c>
       <c r="C154" t="s">
+        <v>471</v>
+      </c>
+      <c r="D154" t="s">
         <v>472</v>
-      </c>
-      <c r="D154" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
@@ -4293,7 +4293,7 @@
         <v>123</v>
       </c>
       <c r="D155" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -4304,10 +4304,10 @@
         <v>25</v>
       </c>
       <c r="C156" t="s">
+        <v>474</v>
+      </c>
+      <c r="D156" t="s">
         <v>475</v>
-      </c>
-      <c r="D156" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -4318,10 +4318,10 @@
         <v>26</v>
       </c>
       <c r="C157" t="s">
+        <v>476</v>
+      </c>
+      <c r="D157" t="s">
         <v>477</v>
-      </c>
-      <c r="D157" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -4332,10 +4332,10 @@
         <v>27</v>
       </c>
       <c r="C158" t="s">
+        <v>478</v>
+      </c>
+      <c r="D158" t="s">
         <v>479</v>
-      </c>
-      <c r="D158" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
@@ -4346,10 +4346,10 @@
         <v>28</v>
       </c>
       <c r="C159" t="s">
+        <v>480</v>
+      </c>
+      <c r="D159" t="s">
         <v>481</v>
-      </c>
-      <c r="D159" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -4360,10 +4360,10 @@
         <v>29</v>
       </c>
       <c r="C160" t="s">
+        <v>482</v>
+      </c>
+      <c r="D160" t="s">
         <v>483</v>
-      </c>
-      <c r="D160" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -4377,7 +4377,7 @@
         <v>381</v>
       </c>
       <c r="D161" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -4388,10 +4388,10 @@
         <v>31</v>
       </c>
       <c r="C162" t="s">
+        <v>485</v>
+      </c>
+      <c r="D162" t="s">
         <v>486</v>
-      </c>
-      <c r="D162" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -4402,10 +4402,10 @@
         <v>32</v>
       </c>
       <c r="C163" t="s">
+        <v>487</v>
+      </c>
+      <c r="D163" t="s">
         <v>488</v>
-      </c>
-      <c r="D163" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
@@ -4416,10 +4416,10 @@
         <v>33</v>
       </c>
       <c r="C164" t="s">
+        <v>489</v>
+      </c>
+      <c r="D164" t="s">
         <v>490</v>
-      </c>
-      <c r="D164" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
@@ -4430,10 +4430,10 @@
         <v>34</v>
       </c>
       <c r="C165" t="s">
+        <v>491</v>
+      </c>
+      <c r="D165" t="s">
         <v>492</v>
-      </c>
-      <c r="D165" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -4444,10 +4444,10 @@
         <v>35</v>
       </c>
       <c r="C166" t="s">
+        <v>493</v>
+      </c>
+      <c r="D166" t="s">
         <v>494</v>
-      </c>
-      <c r="D166" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
@@ -4458,10 +4458,10 @@
         <v>36</v>
       </c>
       <c r="C167" t="s">
+        <v>495</v>
+      </c>
+      <c r="D167" t="s">
         <v>496</v>
-      </c>
-      <c r="D167" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -4472,10 +4472,10 @@
         <v>37</v>
       </c>
       <c r="C168" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D168" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
@@ -4486,10 +4486,10 @@
         <v>38</v>
       </c>
       <c r="C169" t="s">
+        <v>498</v>
+      </c>
+      <c r="D169" t="s">
         <v>499</v>
-      </c>
-      <c r="D169" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
@@ -4500,10 +4500,10 @@
         <v>39</v>
       </c>
       <c r="C170" t="s">
+        <v>500</v>
+      </c>
+      <c r="D170" t="s">
         <v>501</v>
-      </c>
-      <c r="D170" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
@@ -4514,10 +4514,10 @@
         <v>40</v>
       </c>
       <c r="C171" t="s">
+        <v>502</v>
+      </c>
+      <c r="D171" t="s">
         <v>503</v>
-      </c>
-      <c r="D171" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
@@ -4528,10 +4528,10 @@
         <v>41</v>
       </c>
       <c r="C172" t="s">
+        <v>504</v>
+      </c>
+      <c r="D172" t="s">
         <v>505</v>
-      </c>
-      <c r="D172" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
@@ -4542,10 +4542,10 @@
         <v>42</v>
       </c>
       <c r="C173" t="s">
+        <v>506</v>
+      </c>
+      <c r="D173" t="s">
         <v>507</v>
-      </c>
-      <c r="D173" t="s">
-        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -5408,10 +5408,10 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
+        <v>508</v>
+      </c>
+      <c r="D77" t="s">
         <v>509</v>
-      </c>
-      <c r="D77" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -5422,10 +5422,10 @@
         <v>2</v>
       </c>
       <c r="C78" t="s">
+        <v>510</v>
+      </c>
+      <c r="D78" t="s">
         <v>511</v>
-      </c>
-      <c r="D78" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -5436,10 +5436,10 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
+        <v>512</v>
+      </c>
+      <c r="D79" t="s">
         <v>513</v>
-      </c>
-      <c r="D79" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -5450,10 +5450,10 @@
         <v>4</v>
       </c>
       <c r="C80" t="s">
+        <v>514</v>
+      </c>
+      <c r="D80" t="s">
         <v>515</v>
-      </c>
-      <c r="D80" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -5464,10 +5464,10 @@
         <v>5</v>
       </c>
       <c r="C81" t="s">
+        <v>516</v>
+      </c>
+      <c r="D81" t="s">
         <v>517</v>
-      </c>
-      <c r="D81" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -5478,10 +5478,10 @@
         <v>6</v>
       </c>
       <c r="C82" t="s">
+        <v>518</v>
+      </c>
+      <c r="D82" t="s">
         <v>519</v>
-      </c>
-      <c r="D82" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -5492,10 +5492,10 @@
         <v>7</v>
       </c>
       <c r="C83" t="s">
+        <v>520</v>
+      </c>
+      <c r="D83" t="s">
         <v>521</v>
-      </c>
-      <c r="D83" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -5506,10 +5506,10 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
+        <v>522</v>
+      </c>
+      <c r="D84" t="s">
         <v>523</v>
-      </c>
-      <c r="D84" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -5520,10 +5520,10 @@
         <v>9</v>
       </c>
       <c r="C85" t="s">
+        <v>524</v>
+      </c>
+      <c r="D85" t="s">
         <v>525</v>
-      </c>
-      <c r="D85" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -5534,10 +5534,10 @@
         <v>10</v>
       </c>
       <c r="C86" t="s">
+        <v>526</v>
+      </c>
+      <c r="D86" t="s">
         <v>527</v>
-      </c>
-      <c r="D86" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -5548,10 +5548,10 @@
         <v>11</v>
       </c>
       <c r="C87" t="s">
+        <v>528</v>
+      </c>
+      <c r="D87" t="s">
         <v>529</v>
-      </c>
-      <c r="D87" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -5562,10 +5562,10 @@
         <v>11</v>
       </c>
       <c r="C88" t="s">
+        <v>530</v>
+      </c>
+      <c r="D88" t="s">
         <v>531</v>
-      </c>
-      <c r="D88" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -5590,10 +5590,10 @@
         <v>13</v>
       </c>
       <c r="C90" t="s">
+        <v>504</v>
+      </c>
+      <c r="D90" t="s">
         <v>505</v>
-      </c>
-      <c r="D90" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -5604,10 +5604,10 @@
         <v>14</v>
       </c>
       <c r="C91" t="s">
+        <v>532</v>
+      </c>
+      <c r="D91" t="s">
         <v>533</v>
-      </c>
-      <c r="D91" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -5618,10 +5618,10 @@
         <v>15</v>
       </c>
       <c r="C92" t="s">
+        <v>534</v>
+      </c>
+      <c r="D92" t="s">
         <v>535</v>
-      </c>
-      <c r="D92" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -5632,10 +5632,10 @@
         <v>16</v>
       </c>
       <c r="C93" t="s">
+        <v>536</v>
+      </c>
+      <c r="D93" t="s">
         <v>537</v>
-      </c>
-      <c r="D93" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -5646,10 +5646,10 @@
         <v>17</v>
       </c>
       <c r="C94" t="s">
+        <v>538</v>
+      </c>
+      <c r="D94" t="s">
         <v>539</v>
-      </c>
-      <c r="D94" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -5660,10 +5660,10 @@
         <v>18</v>
       </c>
       <c r="C95" t="s">
+        <v>540</v>
+      </c>
+      <c r="D95" t="s">
         <v>541</v>
-      </c>
-      <c r="D95" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -5674,10 +5674,10 @@
         <v>19</v>
       </c>
       <c r="C96" t="s">
+        <v>542</v>
+      </c>
+      <c r="D96" t="s">
         <v>543</v>
-      </c>
-      <c r="D96" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -5688,10 +5688,10 @@
         <v>20</v>
       </c>
       <c r="C97" t="s">
+        <v>544</v>
+      </c>
+      <c r="D97" t="s">
         <v>545</v>
-      </c>
-      <c r="D97" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -5702,10 +5702,10 @@
         <v>21</v>
       </c>
       <c r="C98" t="s">
+        <v>546</v>
+      </c>
+      <c r="D98" t="s">
         <v>547</v>
-      </c>
-      <c r="D98" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -5716,10 +5716,10 @@
         <v>22</v>
       </c>
       <c r="C99" t="s">
+        <v>548</v>
+      </c>
+      <c r="D99" t="s">
         <v>549</v>
-      </c>
-      <c r="D99" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -5730,10 +5730,10 @@
         <v>23</v>
       </c>
       <c r="C100" t="s">
+        <v>550</v>
+      </c>
+      <c r="D100" t="s">
         <v>551</v>
-      </c>
-      <c r="D100" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -5744,10 +5744,10 @@
         <v>24</v>
       </c>
       <c r="C101" t="s">
+        <v>552</v>
+      </c>
+      <c r="D101" t="s">
         <v>553</v>
-      </c>
-      <c r="D101" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -5758,10 +5758,10 @@
         <v>25</v>
       </c>
       <c r="C102" t="s">
+        <v>554</v>
+      </c>
+      <c r="D102" t="s">
         <v>555</v>
-      </c>
-      <c r="D102" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -5772,10 +5772,10 @@
         <v>26</v>
       </c>
       <c r="C103" t="s">
+        <v>556</v>
+      </c>
+      <c r="D103" t="s">
         <v>557</v>
-      </c>
-      <c r="D103" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -5786,10 +5786,10 @@
         <v>27</v>
       </c>
       <c r="C104" t="s">
+        <v>558</v>
+      </c>
+      <c r="D104" t="s">
         <v>559</v>
-      </c>
-      <c r="D104" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -5800,10 +5800,10 @@
         <v>28</v>
       </c>
       <c r="C105" t="s">
+        <v>560</v>
+      </c>
+      <c r="D105" t="s">
         <v>561</v>
-      </c>
-      <c r="D105" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -5814,10 +5814,10 @@
         <v>29</v>
       </c>
       <c r="C106" t="s">
+        <v>562</v>
+      </c>
+      <c r="D106" t="s">
         <v>563</v>
-      </c>
-      <c r="D106" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -5828,234 +5828,234 @@
         <v>30</v>
       </c>
       <c r="C107" t="s">
+        <v>564</v>
+      </c>
+      <c r="D107" t="s">
         <v>565</v>
-      </c>
-      <c r="D107" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B108" s="1">
         <v>31</v>
       </c>
       <c r="C108" t="s">
+        <v>567</v>
+      </c>
+      <c r="D108" t="s">
         <v>568</v>
-      </c>
-      <c r="D108" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B109" s="1">
         <v>32</v>
       </c>
       <c r="C109" t="s">
+        <v>569</v>
+      </c>
+      <c r="D109" t="s">
         <v>570</v>
-      </c>
-      <c r="D109" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B110" s="1">
         <v>33</v>
       </c>
       <c r="C110" t="s">
+        <v>571</v>
+      </c>
+      <c r="D110" t="s">
         <v>572</v>
-      </c>
-      <c r="D110" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B111" s="1">
         <v>34</v>
       </c>
       <c r="C111" t="s">
+        <v>573</v>
+      </c>
+      <c r="D111" t="s">
         <v>574</v>
-      </c>
-      <c r="D111" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B112" s="1">
         <v>35</v>
       </c>
       <c r="C112" t="s">
+        <v>575</v>
+      </c>
+      <c r="D112" t="s">
         <v>576</v>
-      </c>
-      <c r="D112" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B113" s="1">
         <v>36</v>
       </c>
       <c r="C113" t="s">
+        <v>577</v>
+      </c>
+      <c r="D113" t="s">
         <v>578</v>
-      </c>
-      <c r="D113" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B114" s="1">
         <v>37</v>
       </c>
       <c r="C114" t="s">
+        <v>579</v>
+      </c>
+      <c r="D114" t="s">
         <v>580</v>
-      </c>
-      <c r="D114" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B115" s="1">
         <v>38</v>
       </c>
       <c r="C115" t="s">
+        <v>581</v>
+      </c>
+      <c r="D115" t="s">
         <v>582</v>
-      </c>
-      <c r="D115" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B116" s="1">
         <v>39</v>
       </c>
       <c r="C116" t="s">
+        <v>583</v>
+      </c>
+      <c r="D116" t="s">
         <v>584</v>
-      </c>
-      <c r="D116" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B117" s="1">
         <v>40</v>
       </c>
       <c r="C117" t="s">
+        <v>585</v>
+      </c>
+      <c r="D117" t="s">
         <v>586</v>
-      </c>
-      <c r="D117" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B118" s="1">
         <v>41</v>
       </c>
       <c r="C118" t="s">
+        <v>587</v>
+      </c>
+      <c r="D118" t="s">
         <v>588</v>
-      </c>
-      <c r="D118" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B119" s="1">
         <v>42</v>
       </c>
       <c r="C119" t="s">
+        <v>589</v>
+      </c>
+      <c r="D119" t="s">
         <v>590</v>
-      </c>
-      <c r="D119" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B120" s="1">
         <v>43</v>
       </c>
       <c r="C120" t="s">
+        <v>591</v>
+      </c>
+      <c r="D120" t="s">
         <v>592</v>
-      </c>
-      <c r="D120" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B121" s="1">
         <v>44</v>
       </c>
       <c r="C121" t="s">
+        <v>593</v>
+      </c>
+      <c r="D121" t="s">
         <v>594</v>
-      </c>
-      <c r="D121" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B122" s="1">
         <v>45</v>
       </c>
       <c r="C122" t="s">
+        <v>595</v>
+      </c>
+      <c r="D122" t="s">
         <v>596</v>
-      </c>
-      <c r="D122" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B123" s="1">
         <v>46</v>
       </c>
       <c r="C123" t="s">
+        <v>597</v>
+      </c>
+      <c r="D123" t="s">
         <v>598</v>
-      </c>
-      <c r="D123" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
